--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,9 +247,6 @@
   </si>
   <si>
     <t>Mapping: UDI Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -776,10 +776,10 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
+    <t>1367: source value from GENERATOR IMPLANT - TRANSMITTER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (#698-13 &gt; 698.6-.01)</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
-  </si>
-  <si>
-    <t>1367: source value from GENERATOR IMPLANT - TRANSMITTER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (#698-13 &gt; 698.6-.01)</t>
   </si>
   <si>
     <t>Device.manufactureDate</t>
@@ -899,10 +899,10 @@
     <t>The model number for the device.</t>
   </si>
   <si>
+    <t>1389: source value from GENERATOR IMPLANT - TRANSMITTER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (#698-12 &gt; 698.4-.01)</t>
+  </si>
+  <si>
     <t>.softwareName (included as part)</t>
-  </si>
-  <si>
-    <t>1389: source value from GENERATOR IMPLANT - TRANSMITTER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (#698-12 &gt; 698.4-.01)</t>
   </si>
   <si>
     <t>Device.partNumber</t>
@@ -1546,10 +1546,10 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.40234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="164.38671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="164.38671875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="61.40234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1776,10 +1776,10 @@
         <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>77</v>
@@ -2344,10 +2344,10 @@
         <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2458,10 +2458,10 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2572,10 +2572,10 @@
         <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2688,10 +2688,10 @@
         <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL10" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2802,16 +2802,16 @@
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3028,13 +3028,13 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3140,10 +3140,10 @@
         <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3254,10 +3254,10 @@
         <v>136</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3370,10 +3370,10 @@
         <v>136</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3482,16 +3482,16 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3594,16 +3594,16 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -3708,10 +3708,10 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3822,16 +3822,16 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3936,16 +3936,16 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4050,10 +4050,10 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4164,13 +4164,13 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4279,10 +4279,10 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4390,16 +4390,16 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4505,13 +4505,13 @@
         <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>239</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4614,16 +4614,16 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -4726,16 +4726,16 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4838,16 +4838,16 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -4952,13 +4952,13 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5176,10 +5176,10 @@
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5290,10 +5290,10 @@
         <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5406,10 +5406,10 @@
         <v>136</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5630,13 +5630,13 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5745,13 +5745,13 @@
         <v>278</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AN37" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -5856,13 +5856,13 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5966,7 +5966,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5975,7 +5975,7 @@
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -6190,10 +6190,10 @@
         <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6304,10 +6304,10 @@
         <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6420,10 +6420,10 @@
         <v>136</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6647,10 +6647,10 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6868,10 +6868,10 @@
         <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6982,10 +6982,10 @@
         <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7098,10 +7098,10 @@
         <v>136</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7325,10 +7325,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7658,10 +7658,10 @@
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7772,10 +7772,10 @@
         <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7888,10 +7888,10 @@
         <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8338,13 +8338,13 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8450,13 +8450,13 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8564,13 +8564,13 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8678,13 +8678,13 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8792,13 +8792,13 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8904,10 +8904,10 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9016,10 +9016,10 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="427">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,6 +484,194 @@
     <t>The serial number which is a component of the production identifier (PI), a conditional, variable portion of a UDI.   The identifier.type code should be set to “SNO”(Serial Number) and the system left empty.</t>
   </si>
   <si>
+    <t>Device.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Device.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Device.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Device.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>Device.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Device.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1349: source value from GENERATOR IMPLANT - IEN (#698-.001)</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Device.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Device.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>Device.definition</t>
   </si>
   <si>
@@ -519,29 +707,7 @@
     <t>Device.udiCarrier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Device.udiCarrier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -687,9 +853,6 @@
     <t>Supports a way to distinguish hand entered from machine read data.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes to identify how UDI data was entered.</t>
   </si>
   <si>
@@ -717,6 +880,9 @@
     <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
   </si>
   <si>
+    <t>1357: fixed value = #inactive when GENERATOR IMPLANT - EXPLANT DATE (#698-96) case is not NULL</t>
+  </si>
+  <si>
     <t>.statusCode</t>
   </si>
   <si>
@@ -726,17 +892,10 @@
     <t>Device.statusReason</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>online | paused | standby | offline | not-ready | transduc-discon | hw-discon | off</t>
   </si>
   <si>
     <t>Reason for the dtatus of the Device availability.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>The availability status reason of the device.</t>
@@ -776,7 +935,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1367: source value from GENERATOR IMPLANT - TRANSMITTER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (#698-13 &gt; 698.6-.01)</t>
+    <t>1366: source value from GENERATOR IMPLANT - PACEMAKER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (#698-3 &gt; 698.6-.01)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
@@ -837,6 +996,9 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
+    <t>1380: source value from GENERATOR IMPLANT - PACEMAKER SERIAL NUMBER (#698-4)</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=MANU].id</t>
   </si>
   <si>
@@ -899,7 +1061,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1389: source value from GENERATOR IMPLANT - TRANSMITTER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (#698-12 &gt; 698.4-.01)</t>
+    <t>1388: source value from GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (#698-2 &gt; 698.4-.01)</t>
   </si>
   <si>
     <t>.softwareName (included as part)</t>
@@ -926,7 +1088,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFdeviceTypePacemaker</t>
   </si>
   <si>
-    <t>1395: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - TRANSMITTER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (#698-12 &gt; 698.4-1)</t>
+    <t>1394: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (#698-2 &gt; 698.4-1)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1075,6 +1237,9 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
+    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (#698-1)</t>
+  </si>
+  <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
   </si>
   <si>
@@ -1082,10 +1247,6 @@
   </si>
   <si>
     <t>Device.owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Organization responsible for device</t>
@@ -1508,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN67"/>
+  <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.6015625" customWidth="true" bestFit="true"/>
@@ -1530,24 +1691,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.39453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="164.38671875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="61.40234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="161.51171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
@@ -2899,7 +3060,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2911,13 +3072,13 @@
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2928,42 +3089,42 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3001,19 +3162,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3025,16 +3186,16 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3042,10 +3203,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3062,22 +3223,26 @@
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3101,13 +3266,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3125,7 +3290,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3137,13 +3302,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3154,21 +3319,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3177,21 +3342,23 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3215,13 +3382,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3239,25 +3406,25 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3268,45 +3435,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3319,7 +3486,7 @@
         <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>77</v>
@@ -3355,25 +3522,25 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3384,18 +3551,18 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>85</v>
@@ -3410,15 +3577,17 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3431,7 +3600,7 @@
         <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>77</v>
@@ -3467,7 +3636,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3482,28 +3651,28 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3519,16 +3688,16 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3579,7 +3748,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3597,21 +3766,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3631,21 +3800,21 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3693,7 +3862,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3711,7 +3880,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3722,14 +3891,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3745,20 +3914,18 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3807,7 +3974,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3825,25 +3992,25 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3862,16 +4029,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3921,13 +4088,13 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
@@ -3939,21 +4106,21 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3976,18 +4143,16 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4011,13 +4176,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4035,7 +4200,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4047,13 +4212,13 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4064,42 +4229,42 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>134</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4125,13 +4290,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4149,28 +4314,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4178,14 +4343,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4198,22 +4363,26 @@
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4237,31 +4406,31 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="Z24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4273,16 +4442,16 @@
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4301,7 +4470,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>85</v>
@@ -4313,10 +4482,10 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>230</v>
@@ -4324,9 +4493,7 @@
       <c r="M25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4393,10 +4560,10 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>234</v>
@@ -4411,7 +4578,7 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4421,7 +4588,7 @@
         <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>77</v>
@@ -4430,13 +4597,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4502,24 +4669,24 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>239</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>128</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4533,7 +4700,7 @@
         <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
@@ -4542,7 +4709,7 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4551,7 +4718,9 @@
         <v>243</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4599,7 +4768,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4617,13 +4786,13 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -4635,7 +4804,7 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4645,24 +4814,26 @@
         <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4729,25 +4900,25 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4763,18 +4934,20 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4823,7 +4996,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4841,21 +5014,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>234</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4869,7 +5042,7 @@
         <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
@@ -4878,18 +5051,18 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4913,13 +5086,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4937,7 +5110,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4955,10 +5128,10 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -4966,10 +5139,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4980,27 +5153,29 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5025,13 +5200,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>77</v>
+        <v>270</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5049,13 +5224,13 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
@@ -5064,13 +5239,13 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5078,10 +5253,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5092,7 +5267,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5104,13 +5279,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>162</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>163</v>
+        <v>277</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5137,13 +5312,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5161,28 +5336,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5190,24 +5365,24 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5216,16 +5391,16 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>132</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>134</v>
+        <v>284</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5275,75 +5450,71 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5391,53 +5562,53 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -5446,13 +5617,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5503,10 +5674,10 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>85</v>
@@ -5521,21 +5692,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5543,13 +5714,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>77</v>
@@ -5558,13 +5729,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>293</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>271</v>
+        <v>300</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5591,13 +5762,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5615,10 +5786,10 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>85</v>
@@ -5633,21 +5804,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5670,13 +5841,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5727,7 +5898,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5742,24 +5913,24 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5773,7 +5944,7 @@
         <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -5782,16 +5953,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5841,7 +6012,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5856,13 +6027,13 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5870,10 +6041,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5881,13 +6052,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
@@ -5896,13 +6067,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5929,11 +6100,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5951,13 +6124,13 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
@@ -5966,7 +6139,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5980,10 +6153,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5994,7 +6167,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6006,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>289</v>
+        <v>152</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>290</v>
+        <v>153</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6063,25 +6236,25 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>154</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6092,21 +6265,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6118,15 +6291,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6175,25 +6350,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6204,14 +6379,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6224,24 +6399,26 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6289,7 +6466,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6307,7 +6484,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6318,46 +6495,42 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>319</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>171</v>
+        <v>320</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6405,25 +6578,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>173</v>
+        <v>318</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6434,14 +6607,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6460,13 +6633,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6493,13 +6666,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6517,7 +6690,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6535,10 +6708,10 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6546,10 +6719,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6563,7 +6736,7 @@
         <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -6572,13 +6745,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6629,7 +6802,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6644,13 +6817,13 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6658,10 +6831,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6672,7 +6845,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6684,15 +6857,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6741,13 +6916,13 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
@@ -6759,10 +6934,10 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6770,10 +6945,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6781,13 +6956,13 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>77</v>
@@ -6796,13 +6971,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>163</v>
+        <v>338</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6829,13 +7004,11 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6853,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>164</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6865,13 +7038,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6882,14 +7055,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6908,17 +7081,15 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>216</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6967,7 +7138,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>168</v>
+        <v>341</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6979,13 +7150,13 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6996,46 +7167,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7083,25 +7250,25 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7112,21 +7279,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>266</v>
+        <v>130</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7138,15 +7305,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>132</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7195,25 +7364,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>306</v>
+        <v>161</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7224,42 +7393,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7307,28 +7480,28 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>309</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7336,14 +7509,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7362,13 +7535,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7419,7 +7592,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7448,10 +7621,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7462,7 +7635,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7474,13 +7647,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7531,13 +7704,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7552,7 +7725,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7560,10 +7733,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7574,7 +7747,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7586,13 +7759,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>163</v>
+        <v>355</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7643,25 +7816,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>164</v>
+        <v>353</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7672,21 +7845,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7698,17 +7871,15 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7757,25 +7928,25 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7786,14 +7957,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7806,26 +7977,24 @@
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="O56" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -7873,7 +8042,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7891,7 +8060,7 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7902,42 +8071,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>322</v>
+        <v>225</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -7985,25 +8158,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>321</v>
+        <v>227</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8014,21 +8187,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8040,13 +8213,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>325</v>
+        <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8097,13 +8270,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8126,10 +8299,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8140,7 +8313,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8152,13 +8325,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>143</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8209,13 +8382,13 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
@@ -8230,7 +8403,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8238,10 +8411,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8255,7 +8428,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>77</v>
@@ -8264,18 +8437,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>332</v>
+        <v>151</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>366</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8323,10 +8494,10 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>85</v>
@@ -8341,10 +8512,10 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>337</v>
+        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8352,10 +8523,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8366,7 +8537,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8378,13 +8549,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>339</v>
+        <v>216</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8435,13 +8606,13 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8453,10 +8624,10 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8464,10 +8635,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8478,7 +8649,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8490,17 +8661,15 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>345</v>
+        <v>151</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>346</v>
+        <v>152</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8549,28 +8718,28 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>344</v>
+        <v>154</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>349</v>
+        <v>155</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>343</v>
+        <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8578,21 +8747,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -8604,18 +8773,18 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>351</v>
+        <v>131</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>352</v>
+        <v>132</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8663,28 +8832,28 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>355</v>
+        <v>155</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8692,44 +8861,46 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>358</v>
+        <v>225</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>359</v>
+        <v>226</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -8777,28 +8948,28 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>357</v>
+        <v>227</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>361</v>
+        <v>128</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8806,10 +8977,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8817,10 +8988,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -8832,13 +9003,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>363</v>
+        <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8889,13 +9060,13 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
@@ -8907,7 +9078,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -8918,10 +9089,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8941,16 +9112,16 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>222</v>
+        <v>378</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9001,7 +9172,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9019,7 +9190,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9030,10 +9201,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9044,7 +9215,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9056,13 +9227,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>371</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9113,13 +9284,13 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
@@ -9140,8 +9311,912 @@
         <v>77</v>
       </c>
     </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN67">
+  <autoFilter ref="A1:AN75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9151,7 +10226,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI66">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,6 +738,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -838,6 +841,9 @@
     <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
   </si>
   <si>
+    <t>1794: target not supported</t>
+  </si>
+  <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>
   </si>
   <si>
@@ -880,7 +886,7 @@
     <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
   </si>
   <si>
-    <t>1357: fixed value = #inactive when GENERATOR IMPLANT - EXPLANT DATE (#698-96) case is not NULL</t>
+    <t>1355: target not supported</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -920,6 +926,9 @@
     <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
   </si>
   <si>
+    <t>1363: target not supported</t>
+  </si>
+  <si>
     <t>.lotNumberText</t>
   </si>
   <si>
@@ -954,6 +963,9 @@
     <t>The date and time when the device was manufactured.</t>
   </si>
   <si>
+    <t>1371: target not supported</t>
+  </si>
+  <si>
     <t>.existenceTime.low</t>
   </si>
   <si>
@@ -969,6 +981,9 @@
     <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
+    <t>1374: target not supported</t>
+  </si>
+  <si>
     <t>.expirationTime</t>
   </si>
   <si>
@@ -984,6 +999,9 @@
     <t>Lot number assigned by the manufacturer.</t>
   </si>
   <si>
+    <t>1377: target not supported</t>
+  </si>
+  <si>
     <t>Device.serialNumber</t>
   </si>
   <si>
@@ -996,7 +1014,7 @@
     <t>Alphanumeric Maximum 20.</t>
   </si>
   <si>
-    <t>1380: source value from GENERATOR IMPLANT - PACEMAKER SERIAL NUMBER (#698-4)</t>
+    <t>1381: target not supported</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].id</t>
@@ -1009,6 +1027,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -4557,28 +4578,28 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4600,10 +4621,10 @@
         <v>99</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4654,7 +4675,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4672,21 +4693,21 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4712,14 +4733,14 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4768,7 +4789,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4786,7 +4807,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4797,14 +4818,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4823,16 +4844,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4882,7 +4903,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4900,25 +4921,25 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4940,13 +4961,13 @@
         <v>151</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4996,7 +5017,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5011,24 +5032,24 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5054,14 +5075,14 @@
         <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5089,10 +5110,10 @@
         <v>167</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5110,7 +5131,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5128,7 +5149,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5139,10 +5160,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5168,13 +5189,13 @@
         <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5203,10 +5224,10 @@
         <v>167</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5224,7 +5245,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5239,13 +5260,13 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5253,10 +5274,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5282,10 +5303,10 @@
         <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5315,10 +5336,10 @@
         <v>178</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5336,7 +5357,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5357,7 +5378,7 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5365,14 +5386,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5394,13 +5415,13 @@
         <v>151</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5450,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5465,24 +5486,24 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5508,10 +5529,10 @@
         <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5562,7 +5583,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5577,13 +5598,13 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>128</v>
@@ -5591,10 +5612,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5617,13 +5638,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5674,7 +5695,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5689,24 +5710,24 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5729,13 +5750,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5786,7 +5807,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5801,24 +5822,24 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5844,10 +5865,10 @@
         <v>151</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5898,7 +5919,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5913,24 +5934,24 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5956,13 +5977,13 @@
         <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6012,7 +6033,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6027,13 +6048,13 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6041,10 +6062,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6070,10 +6091,10 @@
         <v>216</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6124,7 +6145,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6139,7 +6160,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -6153,10 +6174,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6265,10 +6286,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6379,10 +6400,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6495,14 +6516,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6524,10 +6545,10 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6578,7 +6599,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -6607,10 +6628,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6636,10 +6657,10 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6669,10 +6690,10 @@
         <v>167</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6690,7 +6711,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6708,10 +6729,10 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6719,10 +6740,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6748,10 +6769,10 @@
         <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6802,7 +6823,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6817,13 +6838,13 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6831,10 +6852,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6860,13 +6881,13 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6916,7 +6937,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6934,10 +6955,10 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6945,10 +6966,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6974,10 +6995,10 @@
         <v>173</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7008,7 +7029,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7026,7 +7047,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7041,7 +7062,7 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -7055,10 +7076,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7084,10 +7105,10 @@
         <v>216</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7138,7 +7159,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7167,10 +7188,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7279,10 +7300,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7393,10 +7414,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7509,14 +7530,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7538,10 +7559,10 @@
         <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7592,7 +7613,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7621,10 +7642,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7650,10 +7671,10 @@
         <v>151</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7704,7 +7725,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7725,7 +7746,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7733,10 +7754,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7762,10 +7783,10 @@
         <v>216</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7816,7 +7837,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7845,10 +7866,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7957,10 +7978,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8071,10 +8092,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8187,14 +8208,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8216,10 +8237,10 @@
         <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8270,7 +8291,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8299,10 +8320,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8328,10 +8349,10 @@
         <v>143</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8382,7 +8403,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8403,7 +8424,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8411,10 +8432,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8440,10 +8461,10 @@
         <v>151</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8494,7 +8515,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>85</v>
@@ -8523,10 +8544,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8552,10 +8573,10 @@
         <v>216</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8606,7 +8627,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8635,10 +8656,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8747,10 +8768,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8861,10 +8882,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8977,10 +8998,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9006,10 +9027,10 @@
         <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9060,7 +9081,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>85</v>
@@ -9089,10 +9110,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9115,13 +9136,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9172,7 +9193,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9201,10 +9222,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9230,10 +9251,10 @@
         <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9284,7 +9305,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9313,10 +9334,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9339,17 +9360,17 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9398,7 +9419,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9413,13 +9434,13 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9427,10 +9448,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9456,10 +9477,10 @@
         <v>205</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9510,7 +9531,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9528,10 +9549,10 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9539,10 +9560,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9565,16 +9586,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9624,7 +9645,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9642,10 +9663,10 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9653,10 +9674,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9679,17 +9700,17 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9738,7 +9759,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9756,10 +9777,10 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -9767,10 +9788,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9796,13 +9817,13 @@
         <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9852,7 +9873,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9870,10 +9891,10 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -9881,10 +9902,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9907,13 +9928,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9964,7 +9985,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9982,7 +10003,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9993,10 +10014,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10022,10 +10043,10 @@
         <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10076,7 +10097,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10094,7 +10115,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10105,10 +10126,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10131,13 +10152,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10188,7 +10209,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GENERATOR IMPLANT (#698) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file GENERATOR IMPLANT (698) to us-core-implantable-device</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -628,7 +628,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1349: source value from GENERATOR IMPLANT - IEN (#698-.001)</t>
+    <t>1349: source value from GENERATOR IMPLANT - IEN (698-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -947,7 +947,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1366: source value from GENERATOR IMPLANT - PACEMAKER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (#698-3 &gt; 698.6-.01)</t>
+    <t>1366: source value from GENERATOR IMPLANT - PACEMAKER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (698-3 &gt; 698.6-.01)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
@@ -1085,7 +1085,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1388: source value from GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (#698-2 &gt; 698.4-.01)</t>
+    <t>1388: source value from GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (698-2 &gt; 698.4-.01)</t>
   </si>
   <si>
     <t>.softwareName (included as part)</t>
@@ -1112,7 +1112,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFdeviceTypePacemaker</t>
   </si>
   <si>
-    <t>1394: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (#698-2 &gt; 698.4-1)</t>
+    <t>1394: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (698-2 &gt; 698.4-1)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1261,7 +1261,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (#698-1)</t>
+    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (698-1)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
@@ -1731,7 +1731,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="161.51171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="159.9765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,10 +601,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1349-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -3522,7 +3528,7 @@
         <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>78</v>
@@ -3553,10 +3559,10 @@
         <v>78</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>78</v>
@@ -3592,7 +3598,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3607,13 +3613,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3624,10 +3630,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3653,13 +3659,13 @@
         <v>152</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3673,7 +3679,7 @@
         <v>78</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>78</v>
@@ -3709,7 +3715,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3724,13 +3730,13 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3741,10 +3747,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3767,13 +3773,13 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3824,7 +3830,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3845,7 +3851,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3856,10 +3862,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3882,16 +3888,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3941,7 +3947,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3962,7 +3968,7 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -3973,10 +3979,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3999,13 +4005,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4056,7 +4062,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4088,10 +4094,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4114,16 +4120,16 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4173,7 +4179,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4194,7 +4200,7 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>149</v>
@@ -4205,10 +4211,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4320,10 +4326,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4437,14 +4443,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4466,10 +4472,10 @@
         <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>135</v>
@@ -4524,7 +4530,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4556,14 +4562,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4585,10 +4591,10 @@
         <v>152</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4639,7 +4645,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4654,31 +4660,31 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4700,10 +4706,10 @@
         <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4754,7 +4760,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4775,21 +4781,21 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4815,14 +4821,14 @@
         <v>100</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4871,7 +4877,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4892,7 +4898,7 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4903,14 +4909,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4929,16 +4935,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4988,7 +4994,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5009,25 +5015,25 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5049,13 +5055,13 @@
         <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5105,7 +5111,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5120,27 +5126,27 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5166,14 +5172,14 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5201,10 +5207,10 @@
         <v>168</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5222,7 +5228,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5243,7 +5249,7 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5254,10 +5260,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5283,13 +5289,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5318,10 +5324,10 @@
         <v>168</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5339,7 +5345,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5354,16 +5360,16 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5371,10 +5377,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5400,10 +5406,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5433,10 +5439,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5454,7 +5460,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5478,7 +5484,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5486,14 +5492,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5515,13 +5521,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5571,7 +5577,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5586,27 +5592,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5632,10 +5638,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5686,7 +5692,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5701,16 +5707,16 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>129</v>
@@ -5718,10 +5724,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5744,13 +5750,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5801,7 +5807,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5816,27 +5822,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5859,13 +5865,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5916,7 +5922,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5931,27 +5937,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5977,10 +5983,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6031,7 +6037,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6046,27 +6052,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6092,13 +6098,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6148,7 +6154,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6163,16 +6169,16 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>78</v>
@@ -6180,10 +6186,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6206,13 +6212,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6263,7 +6269,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6278,7 +6284,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6295,10 +6301,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6410,10 +6416,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6527,14 +6533,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6556,10 +6562,10 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>135</v>
@@ -6614,7 +6620,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6646,14 +6652,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6675,10 +6681,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6729,7 +6735,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6761,10 +6767,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6790,10 +6796,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6823,10 +6829,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6844,7 +6850,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6865,10 +6871,10 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -6876,10 +6882,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6905,10 +6911,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6959,7 +6965,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6974,16 +6980,16 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -6991,10 +6997,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7020,13 +7026,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7076,7 +7082,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7097,10 +7103,10 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7108,10 +7114,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7137,10 +7143,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7171,7 +7177,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7189,7 +7195,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7204,7 +7210,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7221,10 +7227,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7247,13 +7253,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7304,7 +7310,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7336,10 +7342,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7451,10 +7457,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7568,14 +7574,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7597,10 +7603,10 @@
         <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>135</v>
@@ -7655,7 +7661,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7687,14 +7693,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7716,10 +7722,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7770,7 +7776,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7802,10 +7808,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7831,10 +7837,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7885,7 +7891,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7909,7 +7915,7 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -7917,10 +7923,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7943,13 +7949,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8000,7 +8006,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8032,10 +8038,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8147,10 +8153,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8264,14 +8270,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8293,10 +8299,10 @@
         <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>135</v>
@@ -8351,7 +8357,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8383,14 +8389,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8412,10 +8418,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8466,7 +8472,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8498,10 +8504,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8527,10 +8533,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8581,7 +8587,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8605,7 +8611,7 @@
         <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8613,10 +8619,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8642,10 +8648,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8696,7 +8702,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8728,10 +8734,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8754,13 +8760,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8811,7 +8817,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8843,10 +8849,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8958,10 +8964,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9075,14 +9081,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9104,10 +9110,10 @@
         <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>135</v>
@@ -9162,7 +9168,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9194,10 +9200,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9223,10 +9229,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9277,7 +9283,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9309,10 +9315,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9335,13 +9341,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9392,7 +9398,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9424,10 +9430,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9453,10 +9459,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9507,7 +9513,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9539,10 +9545,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9565,17 +9571,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9624,7 +9630,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9639,16 +9645,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9656,10 +9662,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9682,13 +9688,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9739,7 +9745,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9760,10 +9766,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9771,10 +9777,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9797,16 +9803,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9856,7 +9862,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9877,10 +9883,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9888,10 +9894,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9914,17 +9920,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9973,7 +9979,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9994,10 +10000,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10005,10 +10011,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10034,13 +10040,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10090,7 +10096,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10111,10 +10117,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10122,10 +10128,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10148,13 +10154,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10205,7 +10211,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10226,7 +10232,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10237,10 +10243,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10266,10 +10272,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10320,7 +10326,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10341,7 +10347,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10352,10 +10358,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10378,13 +10384,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10435,7 +10441,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/698</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1349-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1349-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/698</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,7 +601,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/698</t>
+    <t>http://va.gov/identifiers/$Sta3n/698</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -610,7 +610,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1349-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/698</t>
+    <t>1349-1: fixed value = http://va.gov/identifiers/$Sta3n/698</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1254,7 +1254,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1712,7 +1712,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="52.44140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1267,7 +1267,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (698-1)</t>
+    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT &gt; MEDICAL PATIENT - NAME (698-1 &gt; 690-.01)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1267,7 +1267,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT &gt; MEDICAL PATIENT - NAME (698-1 &gt; 690-.01)</t>
+    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (698-1)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1115,7 +1115,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFdeviceTypePacemaker</t>
+    <t>http://va.gov/fhir/ValueSet/deviceTypePacemaker</t>
   </si>
   <si>
     <t>1394: terminologyMaps using VF_deviceTypePacemaker on GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - TYPE OF EQUIPMENT (698-2 &gt; 698.4-1)</t>
@@ -1727,7 +1727,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.39453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="438">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -893,6 +893,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ImplantableDeviceTransmitter-1356:if is NULL then fixed value #active {null}ImplantableDeviceTransmitter-1357:if is not NULL then fixed value #inactive {null}</t>
   </si>
   <si>
     <t>1355: target not supported</t>
@@ -5357,19 +5361,19 @@
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>277</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5377,10 +5381,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5406,10 +5410,10 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5439,10 +5443,10 @@
         <v>179</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5460,7 +5464,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5484,7 +5488,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5492,14 +5496,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5521,13 +5525,13 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5577,7 +5581,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5592,27 +5596,27 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>237</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5638,10 +5642,10 @@
         <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5692,7 +5696,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5707,13 +5711,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>237</v>
@@ -5724,10 +5728,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5750,13 +5754,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5807,7 +5811,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5822,27 +5826,27 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>237</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5865,13 +5869,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5922,7 +5926,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5937,27 +5941,27 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>237</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5983,10 +5987,10 @@
         <v>152</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6037,7 +6041,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6052,27 +6056,27 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>237</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6098,13 +6102,13 @@
         <v>152</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6154,7 +6158,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6169,13 +6173,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>237</v>
@@ -6186,10 +6190,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6215,10 +6219,10 @@
         <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6269,7 +6273,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6284,7 +6288,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6301,10 +6305,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6416,10 +6420,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6533,10 +6537,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6652,14 +6656,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6681,10 +6685,10 @@
         <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6735,7 +6739,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>86</v>
@@ -6767,10 +6771,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6796,10 +6800,10 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6829,10 +6833,10 @@
         <v>168</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6850,7 +6854,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>86</v>
@@ -6871,7 +6875,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>237</v>
@@ -6882,10 +6886,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6911,10 +6915,10 @@
         <v>152</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6965,7 +6969,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6980,13 +6984,13 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>237</v>
@@ -6997,10 +7001,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7026,13 +7030,13 @@
         <v>152</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7082,7 +7086,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7103,7 +7107,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>237</v>
@@ -7114,10 +7118,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7143,10 +7147,10 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7177,7 +7181,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7195,7 +7199,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7210,7 +7214,7 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7227,10 +7231,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7256,10 +7260,10 @@
         <v>219</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7310,7 +7314,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7342,10 +7346,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7457,10 +7461,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7574,10 +7578,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7693,14 +7697,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7722,10 +7726,10 @@
         <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7776,7 +7780,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>86</v>
@@ -7808,10 +7812,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7837,10 +7841,10 @@
         <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7891,7 +7895,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7923,10 +7927,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7952,10 +7956,10 @@
         <v>219</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8006,7 +8010,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8038,10 +8042,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8153,10 +8157,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8270,10 +8274,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8389,14 +8393,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8418,10 +8422,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8472,7 +8476,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8504,10 +8508,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8533,10 +8537,10 @@
         <v>144</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8587,7 +8591,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8619,10 +8623,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8648,10 +8652,10 @@
         <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8702,7 +8706,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>86</v>
@@ -8734,10 +8738,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8763,10 +8767,10 @@
         <v>219</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8817,7 +8821,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8849,10 +8853,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8964,10 +8968,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9081,10 +9085,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9200,10 +9204,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9229,10 +9233,10 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9283,7 +9287,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>86</v>
@@ -9315,10 +9319,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9341,13 +9345,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9398,7 +9402,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9430,10 +9434,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9459,10 +9463,10 @@
         <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9513,7 +9517,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9545,10 +9549,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9571,17 +9575,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9630,7 +9634,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9645,16 +9649,16 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9662,10 +9666,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9691,10 +9695,10 @@
         <v>208</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9745,7 +9749,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9766,10 +9770,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -9777,10 +9781,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9803,16 +9807,16 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9862,7 +9866,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9883,10 +9887,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -9894,10 +9898,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9920,17 +9924,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9979,7 +9983,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10000,10 +10004,10 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10011,10 +10015,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10040,13 +10044,13 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10096,7 +10100,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10117,10 +10121,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10128,10 +10132,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10154,13 +10158,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10211,7 +10215,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10232,7 +10236,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10243,10 +10247,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10272,10 +10276,10 @@
         <v>174</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10326,7 +10330,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10358,10 +10362,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10384,13 +10388,13 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10441,7 +10445,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -896,7 +896,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ImplantableDeviceTransmitter-1356:if is NULL then fixed value #active {null}ImplantableDeviceTransmitter-1357:if is not NULL then fixed value #inactive {null}</t>
+idt-28-1356:698-96: if is NULL then #active {null}idt-28-1357:698-96: if is not NULL then #inactive {null}</t>
   </si>
   <si>
     <t>1355: target not supported</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GENERATOR IMPLANT (698) to us-core-implantable-device</t>
+    <t>This StructureDefinition contains the maps for VistA file GENERATOR IMPLANT (698) to us-core-implantable-device.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,7 +631,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1349: source value from GENERATOR IMPLANT - IEN (698-.001)</t>
+    <t>1349: source value based on GENERATOR IMPLANT - IEN (698-.001)</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
@@ -893,7 +893,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-idt-28-1356:698-96: if is NULL then #active {null}idt-28-1357:698-96: if is not NULL then #inactive {null}</t>
+idt-28-1356:If (698-96) is is NULL then fixed value #active {null}idt-28-1357:If (698-96) is is not NULL then fixed value #inactive {null}</t>
   </si>
   <si>
     <t>1355: target not supported</t>
@@ -954,7 +954,7 @@
     <t>A name of the manufacturer.</t>
   </si>
   <si>
-    <t>1366: source value from GENERATOR IMPLANT - PACEMAKER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (698-3 &gt; 698.6-.01)</t>
+    <t>1366: source value based on GENERATOR IMPLANT - PACEMAKER MANUFACTURER &gt; PACEMAKER MANUFACTURER - NAME (698-3 &gt; 698.6-.01)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
@@ -1092,7 +1092,7 @@
     <t>The model number for the device.</t>
   </si>
   <si>
-    <t>1388: source value from GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (698-2 &gt; 698.4-.01)</t>
+    <t>1388: source value based on GENERATOR IMPLANT - PACEMAKER MODEL &gt; PACEMAKER EQUIPMENT - MODEL NUMBER/NAME (698-2 &gt; 698.4-.01)</t>
   </si>
   <si>
     <t>.softwareName (included as part)</t>
@@ -1268,7 +1268,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1400: reference from GENERATOR IMPLANT - MEDICAL PATIENT (698-1)</t>
+    <t>1400: reference based on GENERATOR IMPLANT - MEDICAL PATIENT (698-1)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="438">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1114,6 +1114,9 @@
   </si>
   <si>
     <t>The kind or type of device.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_deviceTypePacemaker](ConceptMap-VF-deviceTypePacemaker.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/deviceTypePacemaker</t>
@@ -7037,9 +7040,11 @@
       <c r="X47" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="Y47" s="2"/>
+      <c r="Y47" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -7072,7 +7077,7 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -7086,10 +7091,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7115,10 +7120,10 @@
         <v>218</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7169,7 +7174,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7198,10 +7203,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7310,10 +7315,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7424,10 +7429,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7540,10 +7545,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7569,10 +7574,10 @@
         <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7623,7 +7628,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7652,10 +7657,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7681,10 +7686,10 @@
         <v>151</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7735,7 +7740,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7764,10 +7769,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7793,10 +7798,10 @@
         <v>218</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7847,7 +7852,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7876,10 +7881,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7988,10 +7993,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8102,10 +8107,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8218,10 +8223,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8247,10 +8252,10 @@
         <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8301,7 +8306,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8330,10 +8335,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8359,10 +8364,10 @@
         <v>143</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8413,7 +8418,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8442,10 +8447,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8471,10 +8476,10 @@
         <v>151</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8525,7 +8530,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>85</v>
@@ -8554,10 +8559,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8583,10 +8588,10 @@
         <v>218</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8637,7 +8642,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8666,10 +8671,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8778,10 +8783,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8892,10 +8897,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9008,10 +9013,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9037,10 +9042,10 @@
         <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9091,7 +9096,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>85</v>
@@ -9120,10 +9125,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9146,13 +9151,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9203,7 +9208,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9232,10 +9237,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9261,10 +9266,10 @@
         <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9315,7 +9320,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9344,10 +9349,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9370,17 +9375,17 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9429,7 +9434,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9444,13 +9449,13 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9458,10 +9463,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9487,10 +9492,10 @@
         <v>207</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9541,7 +9546,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9559,10 +9564,10 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9570,10 +9575,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9596,16 +9601,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9655,7 +9660,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9673,10 +9678,10 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9684,10 +9689,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9710,17 +9715,17 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9769,7 +9774,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9787,10 +9792,10 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -9798,10 +9803,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9827,13 +9832,13 @@
         <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9883,7 +9888,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9901,10 +9906,10 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -9912,10 +9917,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9938,13 +9943,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9995,7 +10000,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10013,7 +10018,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10024,10 +10029,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10053,10 +10058,10 @@
         <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10107,7 +10112,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10136,10 +10141,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10162,13 +10167,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10219,7 +10224,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -893,7 +893,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-idt-28-1356:If (698-96) is is NULL then fixed value #active {null}idt-28-1357:If (698-96) is is not NULL then fixed value #inactive {null}</t>
+idt-28-1356:If (698-96) is is NULL then fixed value #active {true}idt-28-1357:If (698-96) is is not NULL then fixed value #inactive {true}</t>
   </si>
   <si>
     <t>1355: target not supported</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1037,9 +1037,6 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
-  </si>
-  <si>
-    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -6173,7 +6170,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -6187,10 +6184,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6299,10 +6296,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6413,10 +6410,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6529,14 +6526,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6558,10 +6555,10 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6612,7 +6609,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -6641,10 +6638,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6670,10 +6667,10 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6703,11 +6700,11 @@
         <v>167</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6724,7 +6721,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6742,7 +6739,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>236</v>
@@ -6753,10 +6750,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6782,10 +6779,10 @@
         <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6836,7 +6833,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6851,10 +6848,10 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>236</v>
@@ -6865,10 +6862,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6894,10 +6891,10 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>318</v>
@@ -6950,7 +6947,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6979,10 +6976,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7008,10 +7005,10 @@
         <v>173</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7041,11 +7038,11 @@
         <v>167</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7062,7 +7059,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7077,7 +7074,7 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -7091,10 +7088,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7120,10 +7117,10 @@
         <v>218</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7174,7 +7171,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7203,10 +7200,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7315,10 +7312,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7429,10 +7426,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7545,14 +7542,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7574,10 +7571,10 @@
         <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7628,7 +7625,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7657,10 +7654,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7686,10 +7683,10 @@
         <v>151</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7740,7 +7737,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7769,10 +7766,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7798,10 +7795,10 @@
         <v>218</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7852,7 +7849,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7881,10 +7878,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7993,10 +7990,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8107,10 +8104,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8223,14 +8220,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8252,10 +8249,10 @@
         <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8306,7 +8303,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8335,10 +8332,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8364,10 +8361,10 @@
         <v>143</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8418,7 +8415,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8447,10 +8444,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8476,10 +8473,10 @@
         <v>151</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8530,7 +8527,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>85</v>
@@ -8559,10 +8556,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8588,10 +8585,10 @@
         <v>218</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8642,7 +8639,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8671,10 +8668,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8783,10 +8780,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8897,10 +8894,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9013,10 +9010,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9042,10 +9039,10 @@
         <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9096,7 +9093,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>85</v>
@@ -9125,10 +9122,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9151,13 +9148,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9208,7 +9205,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9237,10 +9234,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9266,10 +9263,10 @@
         <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9320,7 +9317,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9349,10 +9346,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9375,17 +9372,17 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9434,7 +9431,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9449,13 +9446,13 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9463,10 +9460,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9492,10 +9489,10 @@
         <v>207</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9546,7 +9543,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9564,10 +9561,10 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9575,10 +9572,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9601,16 +9598,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9660,7 +9657,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9678,10 +9675,10 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9689,10 +9686,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9715,17 +9712,17 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9774,7 +9771,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9792,10 +9789,10 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -9803,10 +9800,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9832,13 +9829,13 @@
         <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9888,7 +9885,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9906,10 +9903,10 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -9917,10 +9914,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9943,13 +9940,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10000,7 +9997,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10018,7 +10015,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10029,10 +10026,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10058,10 +10055,10 @@
         <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10112,7 +10109,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10141,10 +10138,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10167,13 +10164,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10224,7 +10221,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1268,7 +1268,7 @@
     <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
-    <t>1400: reference based on GENERATOR IMPLANT - MEDICAL PATIENT (698-1)</t>
+    <t>1400: reference based on GENERATOR IMPLANT - MEDICAL PATIENT &gt; MEDICAL PATIENT - NAME (698-1 &gt; 690-.01)</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceTransmitter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
